--- a/data/trans_dic/IP08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,0</t>
+          <t>3,71; 11,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 15,62</t>
+          <t>6,12; 15,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,43</t>
+          <t>3,09; 10,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,41; 15,19</t>
+          <t>6,38; 15,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 16,43</t>
+          <t>7,69; 16,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 16,65</t>
+          <t>7,34; 16,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,72</t>
+          <t>3,45; 10,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 40,17</t>
+          <t>8,49; 36,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 12,5</t>
+          <t>6,91; 12,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,06; 14,22</t>
+          <t>7,92; 14,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,16</t>
+          <t>4,32; 9,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 25,85</t>
+          <t>8,94; 26,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,14</t>
+          <t>5,45; 11,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 17,47</t>
+          <t>10,07; 17,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,89</t>
+          <t>6,72; 13,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 22,73</t>
+          <t>7,03; 21,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,58</t>
+          <t>9,9; 17,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 18,19</t>
+          <t>10,55; 17,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,45</t>
+          <t>6,19; 12,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 14,44</t>
+          <t>7,32; 13,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 13,25</t>
+          <t>8,5; 13,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 16,68</t>
+          <t>11,25; 16,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,82</t>
+          <t>7,3; 11,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 15,18</t>
+          <t>8,28; 15,43</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,25</t>
+          <t>3,06; 9,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,06; 17,71</t>
+          <t>8,8; 17,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,92</t>
+          <t>3,72; 9,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,96</t>
+          <t>4,36; 12,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 14,8</t>
+          <t>6,85; 15,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 20,02</t>
+          <t>11,35; 20,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,31</t>
+          <t>3,14; 9,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 17,6</t>
+          <t>7,32; 16,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 11,02</t>
+          <t>5,94; 11,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,09; 17,09</t>
+          <t>11,21; 17,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,84</t>
+          <t>3,99; 8,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,75</t>
+          <t>6,63; 12,72</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 15,06</t>
+          <t>7,74; 15,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 13,62</t>
+          <t>6,95; 14,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,4</t>
+          <t>2,84; 8,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 14,16</t>
+          <t>5,83; 13,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 14,64</t>
+          <t>7,57; 14,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 17,47</t>
+          <t>9,7; 18,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,37</t>
+          <t>3,72; 9,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 20,84</t>
+          <t>11,09; 21,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,55; 13,61</t>
+          <t>8,58; 13,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,52</t>
+          <t>9,22; 14,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,63</t>
+          <t>3,88; 7,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,87; 16,04</t>
+          <t>9,65; 15,88</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,17</t>
+          <t>6,51; 10,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 13,54</t>
+          <t>9,95; 13,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,49</t>
+          <t>5,29; 8,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,45</t>
+          <t>7,47; 12,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,54</t>
+          <t>9,66; 13,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,64</t>
+          <t>11,64; 15,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,51</t>
+          <t>5,56; 8,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,49; 17,19</t>
+          <t>10,61; 17,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,32</t>
+          <t>8,77; 11,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,32; 14,19</t>
+          <t>11,25; 14,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,07</t>
+          <t>5,73; 7,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,07</t>
+          <t>9,69; 14,64</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que sufrieron alguna dolencia, enfermedad o impedimento que le ha limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>9765</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14065</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8169</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12006</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17537</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>18027</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>23931</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>27303</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32092</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17878</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>35937</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5147; 16460</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8529; 21140</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4133; 14263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7487; 18239</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11764; 25316</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11356; 25651</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5042; 14655</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>11922; 51701</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>20169; 36454</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>23281; 42351</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12074; 25723</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>23047; 67544</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>15696</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27806</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19596</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21360</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>28359</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>25935</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>44055</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>59228</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39636</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>47295</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10646; 22814</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20775; 36199</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>13887; 26901</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13396; 41297</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21005; 36350</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>23621; 40150</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13878; 28654</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>18533; 34809</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>34631; 54680</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>48385; 71195</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>31486; 51102</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>36728; 68452</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7869</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19870</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9532</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14510</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>20960</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>23236</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>45164</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>18601</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>35469</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4217; 12622</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13670; 26555</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5774; 15259</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8248; 23573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10250; 22478</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18914; 33487</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5200; 15253</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>13564; 31225</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>17071; 31852</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>36077; 56001</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12820; 25908</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>24835; 47625</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>22913</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21128</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10350</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15673</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27677</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>28204</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>45127</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>48805</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22978</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>43877</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>16198; 32146</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14575; 30865</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5870; 16859</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9790; 22931</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15685; 30086</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>20223; 37562</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7654; 18765</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>20100; 38439</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>35734; 56357</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>38527; 60599</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>15978; 31595</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>33711; 55449</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>56243</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>82869</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47647</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>63548</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>99029</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>139721</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>185289</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>99093</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>162578</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>44360; 69145</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70716; 97881</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>37149; 58633</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>49681; 83860</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>69713; 97968</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>87689; 118812</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>41248; 63708</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>80646; 131983</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>123077; 160145</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>164766; 207436</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>82772; 114153</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>138048; 208543</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,86</t>
+          <t>3,99; 11,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 15,17</t>
+          <t>6,44; 14,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 10,67</t>
+          <t>3,12; 11,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 15,55</t>
+          <t>5,9; 15,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 16,54</t>
+          <t>7,89; 15,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 16,58</t>
+          <t>7,71; 17,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,04</t>
+          <t>3,8; 10,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 36,82</t>
+          <t>8,32; 38,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 12,49</t>
+          <t>6,84; 12,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 14,4</t>
+          <t>8,1; 14,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,2</t>
+          <t>4,25; 9,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 26,21</t>
+          <t>8,8; 28,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,69</t>
+          <t>5,5; 11,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,07; 17,54</t>
+          <t>10,21; 17,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,01</t>
+          <t>6,82; 13,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 21,68</t>
+          <t>7,0; 21,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 17,13</t>
+          <t>9,62; 17,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,94</t>
+          <t>10,43; 18,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 12,77</t>
+          <t>6,16; 12,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 13,76</t>
+          <t>7,47; 14,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,42</t>
+          <t>8,62; 13,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 16,55</t>
+          <t>11,07; 16,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,85</t>
+          <t>7,32; 11,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 15,43</t>
+          <t>8,03; 15,1</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,16</t>
+          <t>3,07; 9,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,8; 17,09</t>
+          <t>9,04; 17,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,83</t>
+          <t>3,63; 9,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 12,46</t>
+          <t>3,74; 11,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 15,02</t>
+          <t>6,98; 15,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,35; 20,1</t>
+          <t>11,37; 20,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,2</t>
+          <t>3,24; 8,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 16,85</t>
+          <t>7,64; 17,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 11,08</t>
+          <t>5,85; 10,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,21; 17,39</t>
+          <t>11,29; 17,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,07</t>
+          <t>4,04; 8,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,72</t>
+          <t>6,65; 12,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 15,36</t>
+          <t>7,67; 15,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 14,73</t>
+          <t>7,0; 14,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,16</t>
+          <t>2,87; 7,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 13,65</t>
+          <t>6,3; 13,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 14,53</t>
+          <t>7,48; 14,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 18,02</t>
+          <t>9,53; 17,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,12</t>
+          <t>3,81; 9,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 21,21</t>
+          <t>11,12; 20,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 13,53</t>
+          <t>8,3; 13,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 14,5</t>
+          <t>9,27; 14,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,66</t>
+          <t>3,83; 7,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 15,88</t>
+          <t>9,69; 16,15</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,15</t>
+          <t>6,68; 10,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 13,77</t>
+          <t>9,79; 13,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,35</t>
+          <t>5,3; 8,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,61</t>
+          <t>7,39; 12,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 13,57</t>
+          <t>9,63; 13,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,77</t>
+          <t>11,61; 15,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,59</t>
+          <t>5,45; 8,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,61; 17,37</t>
+          <t>10,59; 17,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,41</t>
+          <t>8,62; 11,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,17</t>
+          <t>11,23; 14,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 7,91</t>
+          <t>5,76; 8,02</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 14,64</t>
+          <t>9,66; 14,09</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5147; 16460</t>
+          <t>5539; 15435</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8529; 21140</t>
+          <t>8981; 20819</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4133; 14263</t>
+          <t>4174; 14996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7487; 18239</t>
+          <t>6919; 18314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11764; 25316</t>
+          <t>12071; 24145</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11356; 25651</t>
+          <t>11932; 26978</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5042; 14655</t>
+          <t>5552; 15499</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11922; 51701</t>
+          <t>11685; 54152</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20169; 36454</t>
+          <t>19965; 36623</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23281; 42351</t>
+          <t>23813; 43222</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12074; 25723</t>
+          <t>11887; 26128</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23047; 67544</t>
+          <t>22683; 72286</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10646; 22814</t>
+          <t>10744; 22578</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20775; 36199</t>
+          <t>21075; 35565</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13887; 26901</t>
+          <t>14111; 27721</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13396; 41297</t>
+          <t>13345; 40380</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21005; 36350</t>
+          <t>20406; 37232</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23621; 40150</t>
+          <t>23344; 40594</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13878; 28654</t>
+          <t>13817; 28745</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18533; 34809</t>
+          <t>18910; 36145</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34631; 54680</t>
+          <t>35130; 55073</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48385; 71195</t>
+          <t>47634; 71213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31486; 51102</t>
+          <t>31549; 51062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>36728; 68452</t>
+          <t>35615; 66977</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4217; 12622</t>
+          <t>4225; 12895</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13670; 26555</t>
+          <t>14052; 27394</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5774; 15259</t>
+          <t>5640; 14770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8248; 23573</t>
+          <t>7068; 21961</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10250; 22478</t>
+          <t>10448; 22841</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18914; 33487</t>
+          <t>18944; 33478</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5200; 15253</t>
+          <t>5378; 14332</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13564; 31225</t>
+          <t>14158; 32675</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17071; 31852</t>
+          <t>16827; 30721</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36077; 56001</t>
+          <t>36339; 55816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12820; 25908</t>
+          <t>12965; 25729</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24835; 47625</t>
+          <t>24895; 48479</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16198; 32146</t>
+          <t>16052; 32673</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14575; 30865</t>
+          <t>14662; 30578</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5870; 16859</t>
+          <t>5926; 16183</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9790; 22931</t>
+          <t>10582; 23257</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15685; 30086</t>
+          <t>15491; 30805</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20223; 37562</t>
+          <t>19870; 36677</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7654; 18765</t>
+          <t>7829; 19742</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20100; 38439</t>
+          <t>20160; 38027</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35734; 56357</t>
+          <t>34551; 55895</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38527; 60599</t>
+          <t>38733; 61736</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15978; 31595</t>
+          <t>15782; 31622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33711; 55449</t>
+          <t>33837; 56396</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44360; 69145</t>
+          <t>45465; 68573</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70716; 97881</t>
+          <t>69593; 97242</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37149; 58633</t>
+          <t>37234; 59554</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49681; 83860</t>
+          <t>49148; 82883</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>69713; 97968</t>
+          <t>69555; 98523</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87689; 118812</t>
+          <t>87486; 116351</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41248; 63708</t>
+          <t>40454; 62554</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80646; 131983</t>
+          <t>80504; 133640</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>123077; 160145</t>
+          <t>120983; 159801</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164766; 207436</t>
+          <t>164447; 205744</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82772; 114153</t>
+          <t>83244; 115865</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>138048; 208543</t>
+          <t>137584; 200782</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP08-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP08-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,04%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,09%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,11%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,24%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 11,13</t>
+          <t>7,57; 16,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 14,94</t>
+          <t>7,73; 16,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,22</t>
+          <t>3,65; 10,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 15,62</t>
+          <t>8,3; 37,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,89; 15,77</t>
+          <t>3,7; 11,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 17,44</t>
+          <t>6,34; 15,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 10,62</t>
+          <t>3,32; 10,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,32; 38,57</t>
+          <t>6,35; 15,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,55</t>
+          <t>6,83; 12,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,7</t>
+          <t>8,06; 14,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,34</t>
+          <t>4,34; 9,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 28,05</t>
+          <t>8,91; 23,88</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,37%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,93%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>8,04%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,47%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>9,48%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 11,57</t>
+          <t>9,85; 17,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 17,23</t>
+          <t>10,13; 18,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,41</t>
+          <t>6,14; 12,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 21,2</t>
+          <t>7,16; 14,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 17,55</t>
+          <t>5,43; 11,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,43; 18,14</t>
+          <t>10,16; 17,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 12,81</t>
+          <t>6,87; 12,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 14,28</t>
+          <t>5,53; 12,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 13,52</t>
+          <t>8,45; 13,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 16,55</t>
+          <t>11,16; 16,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,32; 11,84</t>
+          <t>7,25; 11,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 15,1</t>
+          <t>7,36; 12,18</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15,18%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,71%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,79%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,14%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,36</t>
+          <t>6,64; 14,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,04; 17,63</t>
+          <t>11,21; 20,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,51</t>
+          <t>3,18; 9,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 11,61</t>
+          <t>7,68; 18,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 15,26</t>
+          <t>2,99; 9,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,37; 20,1</t>
+          <t>9,06; 17,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,65</t>
+          <t>3,55; 9,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 17,63</t>
+          <t>6,11; 14,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,69</t>
+          <t>5,69; 11,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 17,34</t>
+          <t>11,09; 17,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,02</t>
+          <t>3,87; 7,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 12,95</t>
+          <t>7,85; 14,17</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10,95%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,08%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,72%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 15,61</t>
+          <t>7,56; 14,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,0; 14,59</t>
+          <t>9,71; 17,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,84</t>
+          <t>3,89; 9,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 13,85</t>
+          <t>10,58; 19,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 14,87</t>
+          <t>7,52; 15,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 17,6</t>
+          <t>6,79; 13,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,6</t>
+          <t>2,86; 8,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 20,98</t>
+          <t>6,23; 14,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 13,42</t>
+          <t>8,55; 13,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 14,77</t>
+          <t>9,26; 14,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,67</t>
+          <t>4,03; 7,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 16,15</t>
+          <t>9,59; 15,31</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,59%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12,72%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,26%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>11,66%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>6,79%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,07</t>
+          <t>9,79; 13,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,68</t>
+          <t>11,36; 15,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,48</t>
+          <t>5,57; 8,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 12,47</t>
+          <t>10,22; 16,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,63; 13,65</t>
+          <t>6,7; 10,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,61; 15,44</t>
+          <t>9,9; 13,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,43</t>
+          <t>5,26; 8,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,59; 17,58</t>
+          <t>7,63; 11,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 11,39</t>
+          <t>8,77; 11,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 14,05</t>
+          <t>11,32; 14,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 8,02</t>
+          <t>5,86; 8,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,09</t>
+          <t>9,47; 13,49</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17537</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18027</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9709</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>9765</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>14065</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>8169</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12006</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>17537</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18027</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9709</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>33144</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5539; 15435</t>
+          <t>11582; 25144</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8981; 20819</t>
+          <t>11963; 25755</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4174; 14996</t>
+          <t>5329; 15637</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6919; 18314</t>
+          <t>10454; 47236</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12071; 24145</t>
+          <t>5139; 15259</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11932; 26978</t>
+          <t>8837; 21771</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5552; 15499</t>
+          <t>4437; 13943</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11685; 54152</t>
+          <t>7693; 18471</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19965; 36623</t>
+          <t>19919; 36465</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23813; 43222</t>
+          <t>23709; 41823</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11887; 26128</t>
+          <t>12149; 25615</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22683; 72286</t>
+          <t>21999; 58983</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28359</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31422</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23307</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>15696</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>27806</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19596</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>21360</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28359</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31422</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20041</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>47295</t>
+          <t>39454</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10744; 22578</t>
+          <t>20887; 37304</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21075; 35565</t>
+          <t>22669; 40727</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14111; 27721</t>
+          <t>13770; 27943</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13345; 40380</t>
+          <t>16817; 33485</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20406; 37232</t>
+          <t>10604; 21744</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23344; 40594</t>
+          <t>20965; 36054</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13817; 28745</t>
+          <t>14210; 26645</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18910; 36145</t>
+          <t>10203; 23131</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35130; 55073</t>
+          <t>34426; 53949</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47634; 71213</t>
+          <t>48022; 71746</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31549; 51062</t>
+          <t>31250; 50964</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35615; 66977</t>
+          <t>30865; 51076</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15366</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25293</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9068</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>19858</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>7869</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>19870</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>9532</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>14510</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>15366</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25293</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>34616</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4225; 12895</t>
+          <t>9945; 22148</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14052; 27394</t>
+          <t>18678; 33352</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5640; 14770</t>
+          <t>5269; 15438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7068; 21961</t>
+          <t>12933; 30662</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10448; 22841</t>
+          <t>4121; 12754</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18944; 33478</t>
+          <t>14077; 27522</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5378; 14332</t>
+          <t>5503; 15403</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14158; 32675</t>
+          <t>9519; 21855</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16827; 30721</t>
+          <t>16355; 31694</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36339; 55816</t>
+          <t>35718; 55026</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12965; 25729</t>
+          <t>12414; 25171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24895; 48479</t>
+          <t>25436; 45944</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22215</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27677</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12629</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25073</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22913</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>21128</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>10350</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22215</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27677</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12629</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>15666</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43877</t>
+          <t>40739</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16052; 32673</t>
+          <t>15658; 30325</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14662; 30578</t>
+          <t>20227; 36410</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5926; 16183</t>
+          <t>7998; 19276</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10582; 23257</t>
+          <t>17921; 33496</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15491; 30805</t>
+          <t>15749; 31523</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19870; 36677</t>
+          <t>14228; 28551</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7829; 19742</t>
+          <t>5912; 17341</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20160; 38027</t>
+          <t>10411; 23432</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34551; 55895</t>
+          <t>35599; 56690</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38733; 61736</t>
+          <t>38711; 60691</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15782; 31622</t>
+          <t>16612; 31471</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>33837; 56396</t>
+          <t>32264; 51505</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>83478</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>102419</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>51447</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>88871</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>56243</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>47647</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>63548</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>83478</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>102419</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51447</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>99029</t>
+          <t>59082</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>162578</t>
+          <t>147953</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45465; 68573</t>
+          <t>70691; 97757</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69593; 97242</t>
+          <t>85622; 117859</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37234; 59554</t>
+          <t>41347; 63119</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49148; 82883</t>
+          <t>71419; 114800</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>69555; 98523</t>
+          <t>45625; 69264</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87486; 116351</t>
+          <t>70360; 96227</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40454; 62554</t>
+          <t>36956; 59632</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>80504; 133640</t>
+          <t>47941; 71961</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>120983; 159801</t>
+          <t>122977; 158856</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>164447; 205744</t>
+          <t>165806; 207696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83244; 115865</t>
+          <t>84660; 116464</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>137584; 200782</t>
+          <t>125646; 178982</t>
         </is>
       </c>
     </row>
